--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0049.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0049.xlsx
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Chính… chính tôi…</t>
+          <t>Là... là tôi...</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Tôi là thằng ngốc đã giặt quần áo bằng mì ăn liền… Chính là tôi…</t>
+          <t>Tao là thằng ngốc đã giặt quần áo chung với mì ăn liền… Chính tao đây…</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Nguồn gốc… Bánh mì tròn… Trắng… Năng lượng… Giấy… Máy…</t>
+          <t>Nguồn gốc… Bánh mì tròn… Trắng… Năng lượng… Giấy… Máy móc…</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Ding, ding, ding… Ding, ding, ding…</t>
+          <t>Ting, ting, ting… Ting, ting, ting…</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Kỳ lạ thật…</t>
+          <t>Kỳ lạ quá…</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Bạn quay lại để xác định phương hướng, nhưng rồi—</t>
+          <t>Bạn quay lại định xác định phương hướng, nhưng rồi—</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Đợi đã, bạn định—</t>
+          <t>Khoan, cậu định—</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Rồi bạn—</t>
+          <t>Vậy là cậu—</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Giá mà chúng ta có thể xin vài Echo từ Hội để hỗ trợ việc canh tác…</t>
+          <t>Giá như chúng ta có thể xin vài Echo từ Hội để giúp việc đồng áng…</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Ngài Bellano, ngài không cho tôi lựa chọn nào khác—</t>
+          <t>Ngài Bellano, ngài buộc ta phải ra tay thôi—</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Hỡi Sentinel, hỡi Sentinel, ngươi—</t>
+          <t>Hỡi Người Bảo Vệ, Người Bảo Vệ ơi, Người—</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Hail Imperator—</t>
+          <t>Bái kiến Hoàng đế—</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Nhưng vì chúng đã tự tìm đến cửa, chúng ta sẽ cho chúng thấy con đường của chúng ta—</t>
+          <t>Nhưng vì chúng đã tự tìm đến cửa, ta sẽ cho chúng thấy cách của chúng ta—</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Dưới đó còn có một mảnh giấy da với vài dòng chữ mà tôi không đọc được—</t>
+          <t>Dưới đó còn có một mảnh giấy da với vài dòng chữ ta không đọc được—</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Tôi hiểu tại sao bạn lại có quan điểm đó, nhưng—</t>
+          <t>Ta hiểu tại sao ngươi lại có quan điểm đó, nhưng—</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>(Kể cho cô ấy về Davide)</t>
+          <t>Kể cho cô ấy nghe về Davide.</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>(Đừng kể cho cô ấy về Davide)</t>
+          <t>(Đừng nói với cô ấy về Davide)</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Con có thể xem trận đấu, nhưng nếu ta bắt gặp con ở bàn cá cược lần nữa—</t>
+          <t>Xem trận đấu thì được, nhưng nếu tao thấy mày lại gần bàn cá cược nữa—</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Tôi biết, nhưng cuộc tấn công này đã được dự đoán trước, nên—</t>
+          <t>Tôi biết, nhưng đây là đợt tấn công đã được dự đoán trước mà—</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Tôi không có thẻ thông hành, nhưng—</t>
+          <t>Tớ không có thẻ thông hành, nhưng—</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Tôi biết lịch trình rất gấp rút, và điều này sẽ ảnh hưởng đến giáo sư—</t>
+          <t>Ta biết lịch trình rất gấp, và điều này sẽ ảnh hưởng đến giáo sư—</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Tôi biết lịch trình rất gấp rút, và điều này sẽ ảnh hưởng đến giáo sư—</t>
+          <t>Ta biết lịch trình rất gấp, và điều này sẽ ảnh hưởng đến giáo sư—</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Nhiệt độ không khí dễ chịu, và độ ẩm đang…</t>
+          <t>Nhiệt độ không khí dễ chịu, còn độ ẩm thì…</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>*Tiếng ngáy*</t>
+          <t>*Tiếng ngáy khò khò*</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>*Tiếng ngáy*</t>
+          <t>*Tiếng ngáy khò khò*</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Đây là dành cho bạn, và người bạn đang ngự trong đó—</t>
+          <t>Cái này dành cho cậu, và cả người bạn đang ngự trong cậu—</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Chuyện gì đang xảy ra ở đây…</t>
+          <t>Chuyện gì đang xảy ra thế này…</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8694,8 +8694,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Tôi sẽ không nói gì đâu…
-NAME_TITLE_002561:::Bạn có thể yên tâm, bảo vệ họ ở đây…</t>
+          <t>Tớ sẽ không nói gì cả…</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8765,7 +8764,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Sigh…</t>
+          <t>Hừm…</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8905,7 +8904,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Bạn đặt những bông hoa trước bia mộ…</t>
+          <t>Cậu đặt những bông hoa trước bia mộ…</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -8975,7 +8974,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Tôi muốn nói rằng…</t>
+          <t>Tôi đã muốn nói ra…</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9045,7 +9044,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Bạn đặt những bông hoa trước bia mộ…</t>
+          <t>Cậu đặt những bông hoa trước bia mộ…</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9115,7 +9114,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Bạn đặt những bông hoa trước bia mộ…</t>
+          <t>Cậu đặt những bông hoa trước bia mộ…</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9185,7 +9184,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Bạn đặt những bông hoa trước bia mộ…</t>
+          <t>Cậu đặt những bông hoa trước bia mộ…</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9255,7 +9254,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Bạn đặt những bông hoa trước bia mộ…</t>
+          <t>Cậu đặt những bông hoa trước bia mộ…</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9325,7 +9324,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Hmm…</t>
+          <t>Hừm…</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9395,7 +9394,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Mây che phủ mặt trăng, người ẩn mình trong bóng tối…</t>
+          <t>Mây che trăng, người náu bóng...</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -10445,7 +10444,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Tôi không ngờ mình thực sự được tham gia cuộc săn này…</t>
+          <t>Tao chưa bao giờ nghĩ mình sẽ thực sự được tham gia cuộc săn...</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10515,7 +10514,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Tôi chỉ mong công việc chúng ta làm thực sự giúp ích cho những người khác ngoài kia…</t>
+          <t>Tớ chỉ mong công việc của chúng ta thực sự giúp ích cho những người khác ngoài kia...</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10585,7 +10584,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Griffrex… ôi, Griffrex…</t>
+          <t>Griffrex à... Griffrex...</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10655,7 +10654,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Chỉ tại cậu làm chúng sợ trước thôi—</t>
+          <t>Chỉ tại cậu dọa chúng trước thôi—</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10725,7 +10724,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Tiếng kêu vững chắc và quyết tâm*</t>
+          <t>*Tiếng hét dứt khoát, kiên định*</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -10795,7 +10794,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Tiếng kêu thận trọng và quyết tâm*</t>
+          <t>*Một tiếng hét thận trọng nhưng quyết tâm*</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -10865,7 +10864,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Tiếng kêu đồng tình*</t>
+          <t>*Tiếng hét đồng tình*</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -10935,7 +10934,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Tiếng hét đầy khí thế</t>
+          <t>*Tiếng hét đầy khí thế*</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11005,7 +11004,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Tiếng hét đầy hứng khởi</t>
+          <t>*Tiếng hét phấn khích*</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11075,7 +11074,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Âm thanh đầy tự hào và vui sướng</t>
+          <t>*Âm thanh hân hoan, đầy tự hào*</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11495,7 +11494,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Ngươi sẽ phải trả giá cho điều này…</t>
+          <t>Cậu sẽ phải trả giá cho việc này…</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11565,7 +11564,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Kẻ chế tạo búp bê, ngươi…</t>
+          <t>Thợ làm búp bê à, cậu…</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11635,7 +11634,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Chúng ta đang ở đâu…</t>
+          <t>Chúng ta đang ở đâu nhỉ…</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -11775,7 +11774,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Ngươi… Gah… *ho*</t>
+          <t>Cậu… Ư… *ho sặc sụa*…</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -11845,7 +11844,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Điều này sẽ vô hiệu hóa hệ thống báo động ở các tầng dưới…</t>
+          <t>Cái này chắc sẽ vô hiệu hóa được hệ thống cảnh báo ở các tầng dưới...</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -12055,7 +12054,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Điều gì thực sự sảng khoái…</t>
+          <t>Thứ thực sự sảng khoái là…</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12335,7 +12334,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Sau khi chúng ta giải quyết ma trận Stellar gây rối đó…</t>
+          <t>Sau khi giải quyết xong cái ma trận Stellar gây rối đó…</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12475,7 +12474,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Và chẳng bao lâu nữa, sẽ có thêm nhiều sân khấu tỏa sáng cho chúng ta, như những vì sao ngày càng rực rỡ hơn…</t>
+          <t>Và chẳng bao lâu nữa, sẽ có thêm nhiều sân khấu rực sáng cho chúng ta, như những vì sao ngày càng tỏa sáng...</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12685,7 +12684,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>(Lắc đầu)</t>
+          <t>Lắc đầu.</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -12755,7 +12754,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Ôi, thật đáng tiếc…</t>
+          <t>Ôi, thật là tiếc...</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -13385,7 +13384,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>******************</t>
+          <t>Chúng ta đang ở đâu vậy...?</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -14365,8 +14364,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>**********************************************************
-NAME_TITLE_0025641::******</t>
+          <t>**********************************************************</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14576,8 +14574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>***********************************************************************************
-```</t>
+          <t>***********************************************************************************</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -14717,7 +14714,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Quá nhiều việc trên tay rồi…</t>
+          <t>Nhiều việc quá rồi đây này…</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -14787,7 +14784,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Thật náo nhiệt quá…</t>
+          <t>Thật sôi động làm sao…</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -17027,7 +17024,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Đừng lại gần nữa, đừng lại gần nữa…</t>
+          <t>Đừng lại gần, đừng lại gần...</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17167,7 +17164,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Không phải chuyến đi biển nào cũng kết thúc với một mẻ cá…</t>
+          <t>Đâu phải chuyến ra khơi nào cũng có cá bắt đâu mà...</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17587,7 +17584,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Sao cô ấy lâu thế nhỉ…</t>
+          <t>Sao cô ấy lâu thế...</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -17657,7 +17654,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Hầu như là do cô ấy thích chiến đấu hơn là thực sự chạy thử nghiệm…</t>
+          <t>Chủ yếu là cô ấy chỉ thích đánh nhau hơn là thực sự làm thí nghiệm…</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -17727,8 +17724,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Bạn và người Làm Vườn tôi vừa gặp…
-NAME_TITLE_002589:::Ý bạn là trước khi đảm nhận vai trò Làm Vườn…</t>
+          <t>Cậu và người Làm Vườn mà ta vừa gặp…</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -17868,7 +17864,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Mỗi Echo háo hức đều bắt chước tiếng vọng của nhau, vọng mãi không dứt—</t>
+          <t>Mỗi Echo háo hức lại vọng theo nhau, vọng mãi không thôi—</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -17938,7 +17934,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Ê, có phải chỉ mình tôi thấy thế không—</t>
+          <t>Ê, có phải chỉ mình tao thấy thế không hay—</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18008,7 +18004,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Đó chính là trí tuệ cổ xưa của Huanglong đấy…</t>
+          <t>Đó chính là trí tuệ cổ xưa của Huanglong...</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18078,7 +18074,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Năng lượng chỉ là phương tiện chứa đựng tính cách và ký ức, chứ không phải nguồn gốc của chúng—</t>
+          <t>Năng lượng chỉ là phương tiện chứa đựng nhân cách và ký ức, chứ không phải nguồn cội của chúng—</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18148,7 +18144,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Tôi từng nghĩ việc tưới cây hàng ngày thật vô nghĩa, nhưng rồi Aalto đã nói với tôi:</t>
+          <t>Tớ từng nghĩ việc tưới cây hàng ngày này chẳng có ý nghĩa gì, cho đến khi Aalto nói với tớ:</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -18288,7 +18284,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Moonlit Path</t>
+          <t>Con Đường Ánh Trăng</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -18358,7 +18354,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Moonlit Path</t>
+          <t>Con Đường Ánh Trăng</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -18428,7 +18424,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Cách Nhận Nhẫn Ánh Trăng</t>
+          <t>Cách lấy Nhẫn Ánh Trăng</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -18498,7 +18494,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Mua để nhận</t>
+          <t>Mua để sở hữu</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -18778,7 +18774,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Purchased</t>
+          <t>Đã mua</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -18848,7 +18844,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Mua để nhận</t>
+          <t>Mua để sở hữu</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -19058,7 +19054,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Tiêu hao</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19128,7 +19124,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Rương Cung Cấp</t>
+          <t>Supply Chest</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -19198,7 +19194,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Phụ kiện tùy chỉnh cho Rover</t>
+          <t>Phụ kiện tùy chỉnh của Vận Mệnh Giả</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -19268,7 +19264,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Custom Livery: Singer in Deepspace</t>
+          <t>Trang Bí Mật Đặc Biệt: Ca Sĩ Vùng Không Gian Sâu</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -19338,7 +19334,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Aemeath - Signature Livery</t>
+          <t>Aemeath - Đồng Phục Đặc Trưng</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -19408,7 +19404,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Bộ bao gồm</t>
+          <t>Bộ này bao gồm</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19478,7 +19474,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Motorbike Accessory: "Little Savior"</t>
+          <t>Phụ Kiện Xe Máy: "Vị Cứu Tinh Nhỏ"</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -19548,7 +19544,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Custom Accessory</t>
+          <t>Trang Sức Tùy Chỉnh</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -21018,7 +21014,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Baichuan</t>
+          <t>Bách Xuyên</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -21088,7 +21084,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Abyssal Mercator</t>
+          <t>Thương Nhân Vực Sâu</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -21158,7 +21154,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Memory of Dreaming</t>
+          <t>Ký Ức Giấc Mơ</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -21228,7 +21224,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Tent</t>
+          <t>Lều trại</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -21298,7 +21294,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Black-Striped Frog</t>
+          <t>Ếch Sọc Đen</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -21368,7 +21364,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Provoke</t>
+          <t>Khiêu khích</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -21648,7 +21644,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Thông báo về Memory Dữ liệu Bị Mất</t>
+          <t>Thông Báo về Mất Dữ Liệu Bộ Nhớ</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -21718,7 +21714,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Control Desk</t>
+          <t>Bàn Điều Khiển</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -21788,7 +21784,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Nervous Roya</t>
+          <t>Roya Lo Lắng</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -21928,7 +21924,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Alptop Champion</t>
+          <t>Nhà Vô Địch Alptop</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -22138,7 +22134,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Qianqian</t>
+          <t>Kiền Kiền</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -22278,7 +22274,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Học sinh Nghỉ ngơi</t>
+          <t>Học sinh Nghỉ Học</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22348,7 +22344,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Cập bến và giao hải sản cho Dana</t>
+          <t>Cập bến và giao cá cho Dana</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -22418,7 +22414,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Cậu Bé Tò Mò</t>
+          <t>Cậu bé tò mò</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -22488,7 +22484,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Qianqian</t>
+          <t>Kiền Kiền</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -22558,7 +22554,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Spacetrek Explorer</t>
+          <t>Nhà thám hiểm Spacetrek</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -22838,7 +22834,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Knight of Ignorance</t>
+          <t>Hiệp Sĩ Vô Tri</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -22908,7 +22904,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Công Dân Kinh Ngạc</t>
+          <t>Người Dân Kinh Ngạc</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -22978,7 +22974,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Cửa Hàng Cung Cấp Mở</t>
+          <t>Mở Cửa Hàng Vật Tư</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -23048,7 +23044,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Zhu Ran</t>
+          <t>Chu Nhiễm</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -23118,7 +23114,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Fireball</t>
+          <t>Quả Cầu Lửa</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23188,7 +23184,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Changli's Weiqi Game</t>
+          <t>Ván cờ vây của Changli</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -23258,7 +23254,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Rapt Shepherd</t>
+          <t>Người Chăn Cừu Đam Mê</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -23328,7 +23324,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Augusta có thể phá hủy 2</t>
+          <t>Augusta có thể bị phá hủy 2</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -23398,7 +23394,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Mutant Organism: Roseshroom Small</t>
+          <t>Sinh Vật Đột Biến: Roseshroom Small</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -23608,7 +23604,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Túi đồ</t>
+          <t>Hành trang</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -23678,7 +23674,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Lính Nam</t>
+          <t>Lính</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -23748,7 +23744,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>test/</t>
+          <t>Thử nghiệm/</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -23958,7 +23954,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Đi Vào Lỗ Đen Dữ Liệu</t>
+          <t>Bước vào Hố Đen Dữ Liệu</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -24098,7 +24094,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Twin Nova: Void Revenant</t>
+          <t>Song Tinh: Hồn Ma Hư Không</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -24168,7 +24164,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Stubborn Researcher</t>
+          <t>Nhà nghiên cứu cứng đầu</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -24238,7 +24234,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Hurriclaw</t>
+          <t>Vuốt Bão Cuồng</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -24308,7 +24304,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Wingray Grapple Base</t>
+          <t>Tia Cánh - Móc Neo Cơ Bản</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -24378,7 +24374,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Acceptance Letter</t>
+          <t>Thư Nhập Học</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -24448,7 +24444,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Uneasy Montelli Member</t>
+          <t>Thành Viên Montelli Bất An</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -24518,7 +24514,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Rotate 90° ngược chiều kim đồng hồ</t>
+          <t>Xoay 90° ngược chiều kim đồng hồ</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24588,7 +24584,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Calm Girl</t>
+          <t>Cô gái bình tĩnh</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -24658,7 +24654,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Phantom: Mourning Aix</t>
+          <t>Hồn Ma: Mourning Aix</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -24728,7 +24724,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Chest Mimic</t>
+          <t>Rương Biến Hình</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -24868,7 +24864,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>"Evil Spirit"</t>
+          <t>"Linh Hồn Quỷ Dữ"</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -25148,7 +25144,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Feiniao</t>
+          <t>Phi Niên</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -25428,7 +25424,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Bulletin Board</t>
+          <t>Bảng tin</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -25498,7 +25494,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Into the dream with Enhancements</t>
+          <t>Đắm chìm vào giấc mơ với Tăng Cường</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -25638,7 +25634,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Khu Vực Thử Thách II</t>
+          <t>Khu vực thử thách II</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -25778,7 +25774,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Thành Viên Fisalia Tuyệt Vọng</t>
+          <t>Thành viên Fisalia Tuyệt vọng</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -25988,7 +25984,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Thành Viên Đoàn Nữ</t>
+          <t>Thành viên nữ đoàn kịch</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -26058,7 +26054,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Nhóm Tự Động</t>
+          <t>Nhóm Tự Động Hóa</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -26128,7 +26124,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Grabbing</t>
+          <t>Nắm rồi</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -26198,7 +26194,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Vận Hành Công Tắc</t>
+          <t>Kích hoạt công tắc</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
@@ -26268,7 +26264,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Jin</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -26338,7 +26334,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Jinlu</t>
+          <t>Kim Lộ</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -26408,7 +26404,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Jinji</t>
+          <t>Jinji!</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -26618,7 +26614,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Main Desk</t>
+          <t>Bàn Lễ Tân Chính</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -26898,7 +26894,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Bắt Đầu Trò Chơi</t>
+          <t>Bắt đầu trò chơi</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -27038,7 +27034,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Tiếp Tục Khám Phá</t>
+          <t>Tiếp tục khám phá</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -27178,7 +27174,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Augusta Realm</t>
+          <t>Thế giới Augusta</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -27248,7 +27244,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Rotate</t>
+          <t>Xoay</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -27318,7 +27314,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>test/</t>
+          <t>Thử nghiệm/</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -27388,7 +27384,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Mô phỏng Chiến thuật</t>
+          <t>Bản Sao Chiến Thuật</t>
         </is>
       </c>
       <c r="N385" t="inlineStr">
@@ -27458,7 +27454,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>"Painter"</t>
+          <t>Họa sĩ</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
@@ -27528,7 +27524,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>TARD-E Unit</t>
+          <t>Đơn vị TARD-E</t>
         </is>
       </c>
       <c r="N387" t="inlineStr">
@@ -27598,7 +27594,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Chi Jiawen</t>
+          <t>Chi Gia Văn</t>
         </is>
       </c>
       <c r="N388" t="inlineStr">
@@ -27668,7 +27664,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Whiff Whaff</t>
+          <t>Phì Phò</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -27738,7 +27734,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Nhà Nghiên Cứu Stellar Matrix</t>
+          <t>Nghiên cứu viên Ma Trận Tinh Tú</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -27878,7 +27874,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Đặt Lại Và Chơi Lại</t>
+          <t>Đặt lại và Phát lại</t>
         </is>
       </c>
       <c r="N392" t="inlineStr">
@@ -27948,7 +27944,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Xem Kết Thúc Lễ Kỷ Niệm</t>
+          <t>Nhìn cái kết của Lễ Hội</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -28018,7 +28014,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Trở Lại Bờ Biển Đen</t>
+          <t>Trở lại Bờ Biển Đen</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -28088,7 +28084,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Pha Chế Đồ Uống</t>
+          <t>Pha đồ uống đi</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -28228,7 +28224,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Pulser</t>
+          <t>Xung Điện</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -28298,7 +28294,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Chàng Trai Bị Thương</t>
+          <t>Thanh Niên Bị Thương</t>
         </is>
       </c>
       <c r="N398" t="inlineStr">
@@ -28368,7 +28364,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Giận Dữ Với Bức Tượng</t>
+          <t>Nổi Giận Trước Bức Tượng</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -28438,7 +28434,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Dungeon_Air Wall Manager_Round</t>
+          <t>Quản lý Rào Cản Không Gian_Vòng</t>
         </is>
       </c>
       <c r="N400" t="inlineStr">
@@ -28508,7 +28504,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Dọn Sạch Chướng Ngại Vật Trên Đường</t>
+          <t>Quét sạch mọi chướng ngại trên đường</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -28648,7 +28644,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Người Phụ Nữ Hoạt Ngôn</t>
+          <t>Người Phụ Nữ Ba Hoa</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28718,7 +28714,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Dân Thường Ngạc Nhiên</t>
+          <t>Người dân ngạc nhiên</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -28788,7 +28784,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Wuchen</t>
+          <t>Vô Trần</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -28998,7 +28994,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Nhà Nghiên Cứu Thư Giãn</t>
+          <t>Nhà Nghiên Cứu Thư Thái</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -29138,7 +29134,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Battery Base</t>
+          <t>Nền Pin</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -29208,7 +29204,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Fractsidus Legion: Pawn</t>
+          <t>Binh Đoàn Fractsidus: Tốt</t>
         </is>
       </c>
       <c r="N411" t="inlineStr">
@@ -29348,7 +29344,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Clay Pot</t>
+          <t>Nồi đất</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -29418,7 +29414,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>KU-Roro Charging Station</t>
+          <t>Jinzhou Harbor</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29558,7 +29554,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Cẩm Nang Du Lịch Septimont Dành Cho Lữ Khách</t>
+          <t>Hướng Dẫn Du Hành Qua Septimont</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -29698,7 +29694,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>: Simulated Replica</t>
+          <t>: Bản Sao Mô Phỏng</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29908,7 +29904,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Sepp</t>
+          <t>Sepp...</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -29978,7 +29974,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Flare Crest 4</t>
+          <t>Huy Hiệu Lửa Cấp 4</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -30048,7 +30044,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Tấn Công Bên Phải</t>
+          <t>Tấn công bên phải</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -30188,7 +30184,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Mảnh Kính Ghép Hình</t>
+          <t>Mảnh Kính Màu</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -30258,7 +30254,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Người Phụ Nữ Royan</t>
+          <t>Phụ Nữ Royan</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30328,7 +30324,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Xoay Bàn Thờ</t>
+          <t>Xoay bàn thờ</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -30398,7 +30394,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Big Bad Demon</t>
+          <t>Con Quỷ Độc Ác</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30468,7 +30464,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Nghỉ Ngơi Một Chút</t>
+          <t>Nghỉ xả hơi chút đi.</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -30538,7 +30534,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Hurriclaw</t>
+          <t>Vuốt Bão Cuồng</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -30608,7 +30604,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Impatient TARD-E Unit</t>
+          <t>Đơn Vị TARD-E Nóng Vội</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30678,7 +30674,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Contaminated Supply Chest</t>
+          <t>Rương Đồ Bị Nhiễm Khuẩn</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -30748,7 +30744,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Kalebyn</t>
+          <t>Kaleb bé nhỏ</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -31028,7 +31024,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Train Echo</t>
+          <t>Hồi Âm Chiến Đấu</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31168,7 +31164,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Enter Sonoro Sphere</t>
+          <t>Vào Sonoro Sphere</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -31238,7 +31234,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Geospider</t>
+          <t>Nhện Địa Chấn</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31448,7 +31444,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Ganxue</t>
+          <t>Cảm Huyết</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31658,7 +31654,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Vào Holy Spire of Confluence</t>
+          <t>Bước vào Thánh Đài Hội Tụ</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -31798,7 +31794,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Cô Bé Lo Lắng</t>
+          <t>Cô Bé Nhỏ Run Rẩy</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -31938,7 +31934,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Mingming</t>
+          <t>Minh Minh</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32008,7 +32004,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Ceaseless Nightmare</t>
+          <t>Ác Mộng Vô Tận</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32078,7 +32074,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Ensemble Sylph</t>
+          <t>Dàn Nhạc Sylph</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -32288,7 +32284,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Pecok Flower</t>
+          <t>Hoa Công Tước</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -32358,7 +32354,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Vào Voidspace</t>
+          <t>Bước vào Không Gian Hư Vô</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -32428,7 +32424,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Worried Female</t>
+          <t>Cô Gái Lo Lắng</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -32568,7 +32564,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Học Sinh Chăm Chỉ</t>
+          <t>Học Giả Chăm Chỉ</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -32638,7 +32634,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Kết Nối Với Cơ Sở Dữ Liệu</t>
+          <t>Kết nối với cơ sở dữ liệu</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -32778,7 +32774,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Cổng Dịch Chuyển Tạm Thời</t>
+          <t>Cổng dịch chuyển tạm thời</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -32988,7 +32984,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Vào Solisylum</t>
+          <t>Bước vào Solisylum</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
@@ -33058,7 +33054,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Remnant Spark</t>
+          <t>Tia Lửa Dư</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -33198,7 +33194,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Tiến Đến Fierce Struggle (Ẩn Dụ)</t>
+          <t>Bước vào cuộc chiến khốc liệt</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33338,7 +33334,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Nhà Nghiên Cứu Vùng Đồng Bằng Dimmr</t>
+          <t>Nhà nghiên cứu Nghiên cứu Đồng bằng Dimmr</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33408,7 +33404,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Ngồi Ghế Gần Mũi Tàu</t>
+          <t>Ngồi ghế gần mũi tàu đi</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -33478,7 +33474,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Gentle Outcast</t>
+          <t>Kẻ lưu lạc hiền hòa</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -33548,7 +33544,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>- Diện Mạo Dục Vọng</t>
+          <t>- Nét Mặt Dục Vọng</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -33618,7 +33614,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Rời khỏi</t>
+          <t>Rời đi</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33758,7 +33754,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Điều Tra Đơn Vị Thí Nghiệm</t>
+          <t>Kiểm tra đơn vị thí nghiệm</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33828,7 +33824,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Nhật ký Bị Loại I</t>
+          <t>Nhật Ký Bị Loại I</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33968,7 +33964,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Stillwind Sundries</t>
+          <t>Cửa Hàng Stillwind</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -34038,7 +34034,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Wuheng</t>
+          <t>Vô Hằng</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -34178,7 +34174,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Old Man's Mirage</t>
+          <t>Huyễn Ảnh Của Lão Già</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -34248,7 +34244,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Mảnh Ghép Câu Đố</t>
+          <t>Bệ Ghép Hình</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -34318,7 +34314,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Green Rabbit with Tail</t>
+          <t>Thỏ Xanh Đuôi Nguyên</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -34458,7 +34454,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Học sinh đói bụng</t>
+          <t>Học sinh đói meo</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -34528,7 +34524,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Talk</t>
+          <t>Nói chuyện</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -34668,7 +34664,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Senior Acolyte</t>
+          <t>Tín Đồ Cao Cấp</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -34738,7 +34734,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Herb Gatherer</t>
+          <t>Người Hái Thảo Dược</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -35158,7 +35154,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Enter "Chaotic Juncture: Spark"</t>
+          <t>Vào "Chaotic Juncture: Spark"</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -35298,7 +35294,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Interaction On</t>
+          <t>Bật tương tác</t>
         </is>
       </c>
       <c r="N498" t="inlineStr">
@@ -35368,7 +35364,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Kiểm tra Sea Apple</t>
+          <t>Kiểm tra Quả Táo Biển</t>
         </is>
       </c>
       <c r="N499" t="inlineStr">
@@ -35438,7 +35434,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Wooden Weiqi Board</t>
+          <t>Bàn Cờ Vây Gỗ</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
